--- a/budget-transfer/ledger/budget_transfer_sheet.xlsx
+++ b/budget-transfer/ledger/budget_transfer_sheet.xlsx
@@ -636,7 +636,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>移管対象部門の予算シートに、移管に必要な列を足したもの。1行＝1案件。投資予算と経費予算が混在する案件は行を分ける。移管するのは予算・契約と、契約に基づく間接業務。直接業務は移管対象部門に残る。今年度から続く投資案件（投資の区分＝継続）は対象外で、移管対象部門に残る。移管判定（AL〜AN）は自動（移管／対象外／判定保留／—）。判定保留は入力が足りないことを示す。案件担当（AY）は進行役が割り当てる。移管ステータス（AP）は案件担当が更新し、「確認（自動）」に判定との食い違いを表示する。予算は全ての案件で一括移管の実施日に移す。経過措置（AO）は、担当の変更に正式な手続きが要るため、手続きが完了するまで今の担当のまま行う間接業務がある案件に「あり」と表示する。薄い色の行は記入例なので、使うときは削除する。</t>
+          <t>移管対象部門の予算シートに、移管に必要な列を足したもの。1行＝1案件。投資予算と経費予算が混在する案件は行を分ける。移管するのは予算・契約と、契約に基づく間接業務。直接業務は移管対象部門に残る。今年度から続く投資案件（投資の区分＝継続）は対象外で、移管対象部門に残る。移管判定（AL〜AN）は自動（移管／対象外／判定保留／—）。判定保留は入力が足りないことを示す。窓口担当（AY）は事務局が割り当てる。移管ステータス（AP）は窓口担当が更新し、「確認（自動）」に判定との食い違いを表示する。予算は全ての案件で一括移管の実施日に移す。経過措置（AO）は、担当の変更に正式な手続きが要るため、手続きが完了するまで今の担当のまま行う間接業務がある案件に「あり」と表示する。薄い色の行は記入例なので、使うときは削除する。</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       <c r="AX4" s="12" t="n"/>
       <c r="AY4" s="12" t="inlineStr">
         <is>
-          <t>案件担当
+          <t>窓口担当
 （IT部門）</t>
         </is>
       </c>
@@ -21372,7 +21372,7 @@
     <row r="57">
       <c r="A57" s="18" t="inlineStr">
         <is>
-          <t>進行役</t>
+          <t>事務局</t>
         </is>
       </c>
       <c r="B57" s="18">
@@ -21399,7 +21399,7 @@
     <row r="58">
       <c r="A58" s="18" t="inlineStr">
         <is>
-          <t>案件担当</t>
+          <t>窓口担当</t>
         </is>
       </c>
       <c r="B58" s="18">
@@ -21558,7 +21558,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>1行＝1件のタスク（対象の部門・案件・契約ごと）。全体と部門の行は進行役が、案件・契約の行は案件担当が作り、自分の行の状態・完了日を更新する。承認の行は、依頼した者（A-03は案件担当、それ以外は進行役）が更新する。役割とタスク名はタスクIDから自動で表示される。期限を過ぎて完了していない行は「期限超過」と表示する。薄い色の行は記入例。</t>
+          <t>1行＝1件のタスク（対象の部門・案件・契約ごと）。全体と部門の行は事務局が、案件・契約の行は窓口担当が作り、自分の行の状態・完了日を更新する。承認の行は、依頼した者（A-03は窓口担当、それ以外は事務局）が更新する。役割とタスク名はタスクIDから自動で表示される。期限を過ぎて完了していない行は「期限超過」と表示する。薄い色の行は記入例。</t>
         </is>
       </c>
     </row>
@@ -50948,7 +50948,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Runbook 全体編（BTR-P-08-00）§2 のタスク一覧を、1行＝1タスクで並べたもの。P-＝進行役、C-＝案件担当、A-＝承認（A-01・A-02・A-04・A-06・A-07・P-05・C-06・C-09 は欠番）。承認（A-）の行は、依頼した者（A-03は案件担当、それ以外は進行役）が承認を得たときに更新する。進捗シートのタスクIDの選択肢になる。手順を変えるときは、先に Runbook と予算移管シート 仕様を直す。</t>
+          <t>Runbook 全体編（BTR-P-08-00）§2 のタスク一覧を、1行＝1タスクで並べたもの。P-＝事務局、C-＝窓口担当、A-＝承認（A-01・A-02・A-04・A-06・A-07・P-05・C-06・C-09 は欠番）。承認（A-）の行は、依頼した者（A-03は窓口担当、それ以外は事務局）が承認を得たときに更新する。進捗シートのタスクIDの選択肢になる。手順を変えるときは、先に Runbook と予算移管シート 仕様を直す。</t>
         </is>
       </c>
     </row>
@@ -50987,17 +50987,17 @@
       </c>
       <c r="B4" s="27" t="inlineStr">
         <is>
-          <t>進行役</t>
+          <t>事務局</t>
         </is>
       </c>
       <c r="C4" s="27" t="inlineStr">
         <is>
-          <t>キックオフを開催する</t>
+          <t>ガイドラインを公開し、説明する</t>
         </is>
       </c>
       <c r="D4" s="27" t="inlineStr">
         <is>
-          <t>進行役編 §3.1</t>
+          <t>事務局編 §3.1</t>
         </is>
       </c>
       <c r="E4" s="27" t="inlineStr">
@@ -51014,17 +51014,17 @@
       </c>
       <c r="B5" s="27" t="inlineStr">
         <is>
-          <t>進行役</t>
+          <t>事務局</t>
         </is>
       </c>
       <c r="C5" s="27" t="inlineStr">
         <is>
-          <t>予算シートを登録し、案件担当を割り当てる</t>
+          <t>予算シートを登録し、窓口担当を割り当てる</t>
         </is>
       </c>
       <c r="D5" s="27" t="inlineStr">
         <is>
-          <t>進行役編 §3.2</t>
+          <t>事務局編 §3.2</t>
         </is>
       </c>
       <c r="E5" s="27" t="inlineStr">
@@ -51041,7 +51041,7 @@
       </c>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>進行役</t>
+          <t>事務局</t>
         </is>
       </c>
       <c r="C6" s="27" t="inlineStr">
@@ -51051,7 +51051,7 @@
       </c>
       <c r="D6" s="27" t="inlineStr">
         <is>
-          <t>進行役編 §3.3</t>
+          <t>事務局編 §3.3</t>
         </is>
       </c>
       <c r="E6" s="27" t="inlineStr">
@@ -51068,7 +51068,7 @@
       </c>
       <c r="B7" s="27" t="inlineStr">
         <is>
-          <t>進行役</t>
+          <t>事務局</t>
         </is>
       </c>
       <c r="C7" s="27" t="inlineStr">
@@ -51078,7 +51078,7 @@
       </c>
       <c r="D7" s="27" t="inlineStr">
         <is>
-          <t>進行役編 §3.4</t>
+          <t>事務局編 §3.4</t>
         </is>
       </c>
       <c r="E7" s="27" t="inlineStr">
@@ -51095,7 +51095,7 @@
       </c>
       <c r="B8" s="27" t="inlineStr">
         <is>
-          <t>進行役</t>
+          <t>事務局</t>
         </is>
       </c>
       <c r="C8" s="27" t="inlineStr">
@@ -51105,7 +51105,7 @@
       </c>
       <c r="D8" s="27" t="inlineStr">
         <is>
-          <t>進行役編 §3.6</t>
+          <t>事務局編 §3.6</t>
         </is>
       </c>
       <c r="E8" s="27" t="inlineStr">
@@ -51122,7 +51122,7 @@
       </c>
       <c r="B9" s="27" t="inlineStr">
         <is>
-          <t>進行役</t>
+          <t>事務局</t>
         </is>
       </c>
       <c r="C9" s="27" t="inlineStr">
@@ -51132,7 +51132,7 @@
       </c>
       <c r="D9" s="27" t="inlineStr">
         <is>
-          <t>進行役編 §3.7</t>
+          <t>事務局編 §3.7</t>
         </is>
       </c>
       <c r="E9" s="27" t="inlineStr">
@@ -51149,7 +51149,7 @@
       </c>
       <c r="B10" s="27" t="inlineStr">
         <is>
-          <t>案件担当</t>
+          <t>窓口担当</t>
         </is>
       </c>
       <c r="C10" s="27" t="inlineStr">
@@ -51159,7 +51159,7 @@
       </c>
       <c r="D10" s="27" t="inlineStr">
         <is>
-          <t>案件担当編 §3.1</t>
+          <t>窓口担当編 §3.1</t>
         </is>
       </c>
       <c r="E10" s="27" t="inlineStr">
@@ -51176,7 +51176,7 @@
       </c>
       <c r="B11" s="27" t="inlineStr">
         <is>
-          <t>案件担当</t>
+          <t>窓口担当</t>
         </is>
       </c>
       <c r="C11" s="27" t="inlineStr">
@@ -51186,7 +51186,7 @@
       </c>
       <c r="D11" s="27" t="inlineStr">
         <is>
-          <t>案件担当編 §3.2</t>
+          <t>窓口担当編 §3.2</t>
         </is>
       </c>
       <c r="E11" s="27" t="inlineStr">
@@ -51203,7 +51203,7 @@
       </c>
       <c r="B12" s="27" t="inlineStr">
         <is>
-          <t>案件担当</t>
+          <t>窓口担当</t>
         </is>
       </c>
       <c r="C12" s="27" t="inlineStr">
@@ -51213,7 +51213,7 @@
       </c>
       <c r="D12" s="27" t="inlineStr">
         <is>
-          <t>案件担当編 §3.3</t>
+          <t>窓口担当編 §3.3</t>
         </is>
       </c>
       <c r="E12" s="27" t="inlineStr">
@@ -51230,7 +51230,7 @@
       </c>
       <c r="B13" s="27" t="inlineStr">
         <is>
-          <t>案件担当</t>
+          <t>窓口担当</t>
         </is>
       </c>
       <c r="C13" s="27" t="inlineStr">
@@ -51240,7 +51240,7 @@
       </c>
       <c r="D13" s="27" t="inlineStr">
         <is>
-          <t>案件担当編 §3.4</t>
+          <t>窓口担当編 §3.4</t>
         </is>
       </c>
       <c r="E13" s="27" t="inlineStr">
@@ -51257,7 +51257,7 @@
       </c>
       <c r="B14" s="27" t="inlineStr">
         <is>
-          <t>案件担当</t>
+          <t>窓口担当</t>
         </is>
       </c>
       <c r="C14" s="27" t="inlineStr">
@@ -51267,7 +51267,7 @@
       </c>
       <c r="D14" s="27" t="inlineStr">
         <is>
-          <t>案件担当編 §3.5</t>
+          <t>窓口担当編 §3.5</t>
         </is>
       </c>
       <c r="E14" s="27" t="inlineStr">
@@ -51284,7 +51284,7 @@
       </c>
       <c r="B15" s="27" t="inlineStr">
         <is>
-          <t>案件担当</t>
+          <t>窓口担当</t>
         </is>
       </c>
       <c r="C15" s="27" t="inlineStr">
@@ -51294,7 +51294,7 @@
       </c>
       <c r="D15" s="27" t="inlineStr">
         <is>
-          <t>案件担当編 §3.7</t>
+          <t>窓口担当編 §3.7</t>
         </is>
       </c>
       <c r="E15" s="27" t="inlineStr">
@@ -51311,7 +51311,7 @@
       </c>
       <c r="B16" s="27" t="inlineStr">
         <is>
-          <t>案件担当</t>
+          <t>窓口担当</t>
         </is>
       </c>
       <c r="C16" s="27" t="inlineStr">
@@ -51321,7 +51321,7 @@
       </c>
       <c r="D16" s="27" t="inlineStr">
         <is>
-          <t>案件担当編 §3.8</t>
+          <t>窓口担当編 §3.8</t>
         </is>
       </c>
       <c r="E16" s="27" t="inlineStr">
@@ -51348,7 +51348,7 @@
       </c>
       <c r="D17" s="27" t="inlineStr">
         <is>
-          <t>案件担当編 §1.5</t>
+          <t>窓口担当編 §1.5</t>
         </is>
       </c>
       <c r="E17" s="27" t="inlineStr">
@@ -51375,7 +51375,7 @@
       </c>
       <c r="D18" s="27" t="inlineStr">
         <is>
-          <t>進行役編 §1.5</t>
+          <t>事務局編 §1.5</t>
         </is>
       </c>
       <c r="E18" s="27" t="inlineStr">
@@ -51402,7 +51402,7 @@
       </c>
       <c r="D19" s="27" t="inlineStr">
         <is>
-          <t>進行役編 §1.5</t>
+          <t>事務局編 §1.5</t>
         </is>
       </c>
       <c r="E19" s="27" t="inlineStr">
